--- a/ExcelProject/Register Student.xlsx
+++ b/ExcelProject/Register Student.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="284">
   <si>
     <t>Execute</t>
   </si>
@@ -85,7 +85,7 @@
     <t>Profile.jpg</t>
   </si>
   <si>
-    <t>ลงทะเบียนสำเร็จ! กรุณาเข้าสู่ระบบ</t>
+    <t>ลงทะเบียนสำเร็จ กรุณาเข้าสู่ระบบ</t>
   </si>
   <si>
     <t>Pass</t>
@@ -484,7 +484,7 @@
     <t>MJU6504106411</t>
   </si>
   <si>
-    <t>เบอร์โทรต้องขึ้นต้นด้วย 06, 07, 08 หรือ 09 และมี 10 หลักเท่านั้น</t>
+    <t>เบอร์โทรต้องขึ้นต้นด้วย 06,07,08,09 และมี 10 หลักเท่านั้น</t>
   </si>
   <si>
     <t>TC2:37</t>
@@ -652,10 +652,14 @@
     <t>Fail</t>
   </si>
   <si>
+    <t xml:space="preserve">Fail
+</t>
+  </si>
+  <si>
     <t>TC2:55</t>
   </si>
   <si>
-    <t>MJU6504106337</t>
+    <t>MJU6504106430</t>
   </si>
   <si>
     <t>TC2:56</t>
@@ -670,7 +674,7 @@
     <t>TC2:57</t>
   </si>
   <si>
-    <t>mju6504106435</t>
+    <t>mju6504106432</t>
   </si>
   <si>
     <t>TC2:58</t>
@@ -682,7 +686,7 @@
     <t>TC2:59</t>
   </si>
   <si>
-    <t>mju65041064001</t>
+    <t>mju65041064341</t>
   </si>
   <si>
     <t>TC2:60</t>
@@ -706,7 +710,7 @@
     <t>รหัสผ่าน</t>
   </si>
   <si>
-    <t>รหัสผ่านอนุญาตเฉพาะ A-Z, a-z, 0-9 และ ! # _ .</t>
+    <t>รหัสผ่านอนุญาตเฉพาะ A-Z,a-z,0-9 และ ! # _ .</t>
   </si>
   <si>
     <t>TC2:63</t>
@@ -823,9 +827,6 @@
     <t>Profile.docx</t>
   </si>
   <si>
-    <t>ไฟล์ต้องเป็น .jpg, .jpeg, .png หรือ .gif เท่านั้น</t>
-  </si>
-  <si>
     <t>* ไฟล์ต้องเป็น .jpg, .jpeg, .png หรือ .gif เท่านั้น</t>
   </si>
   <si>
@@ -856,9 +857,6 @@
     <t>Profile3.jpg</t>
   </si>
   <si>
-    <t>ขนาดไฟล์ต้องไม่เกิน 5MB</t>
-  </si>
-  <si>
     <t>* ขนาดไฟล์ต้องไม่เกิน 5MB</t>
   </si>
   <si>
@@ -868,7 +866,7 @@
     <t>MJU6504106454</t>
   </si>
   <si>
-    <t>กรุณาเลือกไฟล์รูปภาพ</t>
+    <t>* กรุณาเลือกไฟล์รูปภาพ</t>
   </si>
 </sst>
 </file>
@@ -926,7 +924,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -949,11 +947,18 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -994,6 +999,15 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1004,7 +1018,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1308,23 +1322,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="15" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="15" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="8.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="9.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="15" width="10.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="15" width="19.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="15" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="15" width="9.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="15" width="48.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="15" width="41.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="15" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="15" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="18" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="19" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="18" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="19" width="8.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="20" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="18" width="10.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="18" width="19.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="18" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="18" width="9.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="18" width="48.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="18" width="41.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
@@ -1411,7 +1425,9 @@
       <c r="M2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="6"/>
+      <c r="N2" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
       <c r="A3" s="4" t="s">
@@ -1453,7 +1469,9 @@
       <c r="M3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="6"/>
+      <c r="N3" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
       <c r="A4" s="4" t="s">
@@ -1495,7 +1513,9 @@
       <c r="M4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="6"/>
+      <c r="N4" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
       <c r="A5" s="4" t="s">
@@ -1537,7 +1557,9 @@
       <c r="M5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="6"/>
+      <c r="N5" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
       <c r="A6" s="4" t="s">
@@ -1579,7 +1601,9 @@
       <c r="M6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="6"/>
+      <c r="N6" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
       <c r="A7" s="4" t="s">
@@ -1621,7 +1645,9 @@
       <c r="M7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N7" s="6"/>
+      <c r="N7" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
       <c r="A8" s="4" t="s">
@@ -1663,7 +1689,9 @@
       <c r="M8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="6"/>
+      <c r="N8" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
       <c r="A9" s="4" t="s">
@@ -1703,7 +1731,9 @@
       <c r="M9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="6"/>
+      <c r="N9" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
       <c r="A10" s="4" t="s">
@@ -1745,7 +1775,9 @@
       <c r="M10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="6"/>
+      <c r="N10" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
       <c r="A11" s="4" t="s">
@@ -1787,7 +1819,9 @@
       <c r="M11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N11" s="6"/>
+      <c r="N11" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
       <c r="A12" s="4" t="s">
@@ -1829,7 +1863,9 @@
       <c r="M12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="6"/>
+      <c r="N12" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75">
       <c r="A13" s="4" t="s">
@@ -1871,7 +1907,9 @@
       <c r="M13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N13" s="6"/>
+      <c r="N13" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
       <c r="A14" s="4" t="s">
@@ -1913,7 +1951,9 @@
       <c r="M14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="6"/>
+      <c r="N14" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
       <c r="A15" s="4" t="s">
@@ -1955,7 +1995,9 @@
       <c r="M15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="6"/>
+      <c r="N15" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
       <c r="A16" s="4" t="s">
@@ -1997,7 +2039,9 @@
       <c r="M16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
       <c r="A17" s="4" t="s">
@@ -2039,7 +2083,9 @@
       <c r="M17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="6"/>
+      <c r="N17" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21.75">
       <c r="A18" s="4" t="s">
@@ -2081,7 +2127,9 @@
       <c r="M18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N18" s="6"/>
+      <c r="N18" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="21.75">
       <c r="A19" s="4" t="s">
@@ -2123,7 +2171,9 @@
       <c r="M19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N19" s="6"/>
+      <c r="N19" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21.75">
       <c r="A20" s="4" t="s">
@@ -2165,7 +2215,9 @@
       <c r="M20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="6"/>
+      <c r="N20" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21.75">
       <c r="A21" s="4" t="s">
@@ -2205,7 +2257,9 @@
       <c r="M21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N21" s="6"/>
+      <c r="N21" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21.75">
       <c r="A22" s="4" t="s">
@@ -2247,7 +2301,9 @@
       <c r="M22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N22" s="6"/>
+      <c r="N22" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="21.75">
       <c r="A23" s="4" t="s">
@@ -2289,7 +2345,9 @@
       <c r="M23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N23" s="6"/>
+      <c r="N23" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="21.75">
       <c r="A24" s="4" t="s">
@@ -2331,9 +2389,11 @@
       <c r="M24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N24" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21.75">
+      <c r="N24" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21">
       <c r="A25" s="4" t="s">
         <v>14</v>
       </c>
@@ -2373,9 +2433,11 @@
       <c r="M25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N25" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="21.75">
+      <c r="N25" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="21">
       <c r="A26" s="4" t="s">
         <v>14</v>
       </c>
@@ -2415,9 +2477,11 @@
       <c r="M26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N26" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="21.75">
+      <c r="N26" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="21">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2457,9 +2521,11 @@
       <c r="M27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N27" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="21.75">
+      <c r="N27" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="21">
       <c r="A28" s="4" t="s">
         <v>14</v>
       </c>
@@ -2499,9 +2565,11 @@
       <c r="M28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N28" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="21.75">
+      <c r="N28" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="21">
       <c r="A29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2541,9 +2609,11 @@
       <c r="M29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="21.75">
+      <c r="N29" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="21">
       <c r="A30" s="4" t="s">
         <v>14</v>
       </c>
@@ -2583,9 +2653,11 @@
       <c r="M30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N30" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="21.75">
+      <c r="N30" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="21">
       <c r="A31" s="4" t="s">
         <v>14</v>
       </c>
@@ -2625,9 +2697,11 @@
       <c r="M31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N31" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="21.75">
+      <c r="N31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="21">
       <c r="A32" s="4" t="s">
         <v>14</v>
       </c>
@@ -2667,9 +2741,11 @@
       <c r="M32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="21.75">
+      <c r="N32" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="21">
       <c r="A33" s="4" t="s">
         <v>14</v>
       </c>
@@ -2709,9 +2785,11 @@
       <c r="M33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N33" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="21.75">
+      <c r="N33" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="21">
       <c r="A34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2751,7 +2829,9 @@
       <c r="M34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N34" s="6"/>
+      <c r="N34" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="21.75">
       <c r="A35" s="4" t="s">
@@ -2791,7 +2871,9 @@
       <c r="M35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N35" s="6"/>
+      <c r="N35" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="21.75">
       <c r="A36" s="4" t="s">
@@ -2833,7 +2915,9 @@
       <c r="M36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N36" s="6"/>
+      <c r="N36" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="21.75">
       <c r="A37" s="4" t="s">
@@ -2875,7 +2959,9 @@
       <c r="M37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N37" s="6"/>
+      <c r="N37" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="21.75">
       <c r="A38" s="4" t="s">
@@ -2917,7 +3003,9 @@
       <c r="M38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N38" s="6"/>
+      <c r="N38" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="21.75">
       <c r="A39" s="4" t="s">
@@ -2959,7 +3047,9 @@
       <c r="M39" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N39" s="6"/>
+      <c r="N39" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="21.75">
       <c r="A40" s="4" t="s">
@@ -3001,7 +3091,9 @@
       <c r="M40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N40" s="6"/>
+      <c r="N40" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="21.75">
       <c r="A41" s="4" t="s">
@@ -3043,7 +3135,9 @@
       <c r="M41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N41" s="6"/>
+      <c r="N41" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="21.75">
       <c r="A42" s="4" t="s">
@@ -3085,7 +3179,9 @@
       <c r="M42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N42" s="6"/>
+      <c r="N42" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="21.75">
       <c r="A43" s="4" t="s">
@@ -3169,7 +3265,9 @@
       <c r="M44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N44" s="6"/>
+      <c r="N44" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="21.75">
       <c r="A45" s="4" t="s">
@@ -3211,7 +3309,9 @@
       <c r="M45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="6"/>
+      <c r="N45" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="21.75">
       <c r="A46" s="4" t="s">
@@ -3253,7 +3353,9 @@
       <c r="M46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N46" s="6"/>
+      <c r="N46" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="21.75">
       <c r="A47" s="4" t="s">
@@ -3295,7 +3397,9 @@
       <c r="M47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N47" s="6"/>
+      <c r="N47" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="21.75">
       <c r="A48" s="4" t="s">
@@ -3335,7 +3439,9 @@
       <c r="M48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N48" s="6"/>
+      <c r="N48" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="21.75">
       <c r="A49" s="4" t="s">
@@ -3377,7 +3483,9 @@
       <c r="M49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N49" s="6"/>
+      <c r="N49" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="21.75">
       <c r="A50" s="4" t="s">
@@ -3419,7 +3527,9 @@
       <c r="M50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N50" s="6"/>
+      <c r="N50" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="21.75">
       <c r="A51" s="4" t="s">
@@ -3461,7 +3571,9 @@
       <c r="M51" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N51" s="6"/>
+      <c r="N51" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="21.75">
       <c r="A52" s="4" t="s">
@@ -3503,7 +3615,9 @@
       <c r="M52" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N52" s="6"/>
+      <c r="N52" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="21.75">
       <c r="A53" s="4" t="s">
@@ -3545,7 +3659,9 @@
       <c r="M53" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N53" s="6"/>
+      <c r="N53" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="21.75">
       <c r="A54" s="4" t="s">
@@ -3587,7 +3703,9 @@
       <c r="M54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N54" s="6"/>
+      <c r="N54" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="21.75">
       <c r="A55" s="4" t="s">
@@ -3629,14 +3747,16 @@
       <c r="M55" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="N55" s="6"/>
+      <c r="N55" s="6" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="21.75">
       <c r="A56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C56" s="2">
         <v>6504106430</v>
@@ -3654,7 +3774,7 @@
         <v>19</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>21</v>
@@ -3666,19 +3786,21 @@
         <v>23</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N56" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="21.75">
       <c r="A57" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C57" s="2">
         <v>6504106431</v>
@@ -3696,7 +3818,7 @@
         <v>19</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>21</v>
@@ -3705,22 +3827,24 @@
         <v>22</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N57" s="6"/>
+      <c r="N57" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="21.75">
       <c r="A58" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C58" s="2">
         <v>6504106432</v>
@@ -3738,7 +3862,7 @@
         <v>19</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>21</v>
@@ -3755,14 +3879,16 @@
       <c r="M58" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N58" s="6"/>
+      <c r="N58" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="21.75">
       <c r="A59" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C59" s="2">
         <v>6504106433</v>
@@ -3780,7 +3906,7 @@
         <v>19</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>21</v>
@@ -3797,14 +3923,16 @@
       <c r="M59" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N59" s="6"/>
+      <c r="N59" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="21.75">
       <c r="A60" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C60" s="2">
         <v>6504106434</v>
@@ -3822,7 +3950,7 @@
         <v>19</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>21</v>
@@ -3839,14 +3967,16 @@
       <c r="M60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N60" s="6"/>
+      <c r="N60" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="21.75">
       <c r="A61" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C61" s="2">
         <v>6504106435</v>
@@ -3871,22 +4001,24 @@
         <v>22</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N61" s="6"/>
+      <c r="N61" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="21.75">
       <c r="A62" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C62" s="2">
         <v>6504106436</v>
@@ -3904,7 +4036,7 @@
         <v>19</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>21</v>
@@ -3921,14 +4053,16 @@
       <c r="M62" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N62" s="6"/>
+      <c r="N62" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="21.75">
       <c r="A63" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C63" s="2">
         <v>6504106437</v>
@@ -3946,31 +4080,33 @@
         <v>19</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N63" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="21.75">
+      <c r="N63" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="21">
       <c r="A64" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C64" s="2">
         <v>6504106438</v>
@@ -3988,10 +4124,10 @@
         <v>19</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>22</v>
@@ -4005,14 +4141,16 @@
       <c r="M64" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N64" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="21.75">
+      <c r="N64" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="21">
       <c r="A65" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C65" s="2">
         <v>6504106439</v>
@@ -4030,10 +4168,10 @@
         <v>19</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>22</v>
@@ -4047,14 +4185,16 @@
       <c r="M65" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N65" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="21.75">
+      <c r="N65" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="21">
       <c r="A66" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C66" s="2">
         <v>6504106440</v>
@@ -4072,10 +4212,10 @@
         <v>19</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>22</v>
@@ -4089,14 +4229,16 @@
       <c r="M66" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N66" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="21.75">
+      <c r="N66" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="21">
       <c r="A67" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C67" s="2">
         <v>6504106441</v>
@@ -4114,10 +4256,10 @@
         <v>19</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>22</v>
@@ -4131,14 +4273,16 @@
       <c r="M67" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N67" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="21.75">
+      <c r="N67" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="21">
       <c r="A68" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C68" s="2">
         <v>6504106442</v>
@@ -4156,31 +4300,33 @@
         <v>19</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N68" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="21.75">
+      <c r="N68" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="21">
       <c r="A69" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C69" s="2">
         <v>6504106443</v>
@@ -4198,31 +4344,33 @@
         <v>19</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N69" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="21.75">
+      <c r="N69" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="21">
       <c r="A70" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C70" s="2">
         <v>6504106444</v>
@@ -4240,7 +4388,7 @@
         <v>19</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>21</v>
@@ -4257,14 +4405,16 @@
       <c r="M70" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N70" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="21.75">
+      <c r="N70" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="21">
       <c r="A71" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C71" s="2">
         <v>6504106445</v>
@@ -4282,10 +4432,10 @@
         <v>19</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>22</v>
@@ -4299,14 +4449,16 @@
       <c r="M71" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N71" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="21.75">
+      <c r="N71" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="21">
       <c r="A72" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C72" s="2">
         <v>6504106446</v>
@@ -4324,10 +4476,10 @@
         <v>19</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>22</v>
@@ -4341,14 +4493,16 @@
       <c r="M72" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N72" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="21.75">
+      <c r="N72" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="21">
       <c r="A73" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C73" s="2">
         <v>6504106447</v>
@@ -4366,31 +4520,33 @@
         <v>19</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N73" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="21.75">
+      <c r="N73" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="21">
       <c r="A74" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C74" s="2">
         <v>6504106448</v>
@@ -4408,29 +4564,31 @@
         <v>19</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I74" s="13"/>
       <c r="J74" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N74" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="21.75">
+      <c r="N74" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="21">
       <c r="A75" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C75" s="2">
         <v>6504106449</v>
@@ -4448,7 +4606,7 @@
         <v>19</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>21</v>
@@ -4465,14 +4623,16 @@
       <c r="M75" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N75" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="21.75">
+      <c r="N75" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="21">
       <c r="A76" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C76" s="2">
         <v>6504106450</v>
@@ -4490,26 +4650,28 @@
         <v>19</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>21</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>270</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N76" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="21.75">
+        <v>24</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="21">
       <c r="A77" s="4" t="s">
         <v>14</v>
       </c>
@@ -4544,12 +4706,14 @@
         <v>23</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N77" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="21.75">
       <c r="A78" s="4" t="s">
@@ -4586,12 +4750,14 @@
         <v>23</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N78" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="21.75">
       <c r="A79" s="4" t="s">
@@ -4628,19 +4794,21 @@
         <v>280</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N79" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="22.5">
       <c r="A80" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C80" s="2">
         <v>6504106454</v>
@@ -4658,22 +4826,296 @@
         <v>19</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>21</v>
       </c>
       <c r="J80" s="13"/>
       <c r="K80" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>44</v>
+        <v>283</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N80" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
+      <c r="A81" s="14"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="15"/>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
+      <c r="L81" s="15"/>
+      <c r="M81" s="15"/>
+      <c r="N81" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
+      <c r="A82" s="14"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="15"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
+      <c r="L82" s="15"/>
+      <c r="M82" s="15"/>
+      <c r="N82" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
+      <c r="A83" s="14"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
+      <c r="L83" s="15"/>
+      <c r="M83" s="15"/>
+      <c r="N83" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
+      <c r="A84" s="14"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="15"/>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="15"/>
+      <c r="L84" s="15"/>
+      <c r="M84" s="15"/>
+      <c r="N84" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
+      <c r="A85" s="14"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="15"/>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="15"/>
+      <c r="K85" s="15"/>
+      <c r="L85" s="15"/>
+      <c r="M85" s="15"/>
+      <c r="N85" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
+      <c r="A86" s="14"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="15"/>
+      <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
+      <c r="J86" s="15"/>
+      <c r="K86" s="15"/>
+      <c r="L86" s="15"/>
+      <c r="M86" s="15"/>
+      <c r="N86" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
+      <c r="A87" s="14"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="15"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
+      <c r="L87" s="15"/>
+      <c r="M87" s="15"/>
+      <c r="N87" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
+      <c r="A88" s="14"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="15"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+      <c r="L88" s="15"/>
+      <c r="M88" s="15"/>
+      <c r="N88" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
+      <c r="A89" s="14"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="15"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="15"/>
+      <c r="K89" s="15"/>
+      <c r="L89" s="15"/>
+      <c r="M89" s="15"/>
+      <c r="N89" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
+      <c r="A90" s="14"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="15"/>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
+      <c r="L90" s="15"/>
+      <c r="M90" s="15"/>
+      <c r="N90" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
+      <c r="A91" s="14"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="15"/>
+      <c r="M91" s="15"/>
+      <c r="N91" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
+      <c r="A92" s="14"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="15"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
+      <c r="L92" s="15"/>
+      <c r="M92" s="15"/>
+      <c r="N92" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
+      <c r="A93" s="14"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="15"/>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="15"/>
+      <c r="M93" s="15"/>
+      <c r="N93" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
+      <c r="A94" s="14"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="15"/>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
+      <c r="L94" s="15"/>
+      <c r="M94" s="15"/>
+      <c r="N94" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
+      <c r="A95" s="14"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="15"/>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
+      <c r="L95" s="15"/>
+      <c r="M95" s="15"/>
+      <c r="N95" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
+      <c r="A96" s="14"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="15"/>
+      <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
+      <c r="J96" s="15"/>
+      <c r="K96" s="15"/>
+      <c r="L96" s="15"/>
+      <c r="M96" s="15"/>
+      <c r="N96" s="15"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
+      <c r="A97" s="14"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="15"/>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
+      <c r="L97" s="15"/>
+      <c r="M97" s="15"/>
+      <c r="N97" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelProject/Register Student.xlsx
+++ b/ExcelProject/Register Student.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="285">
   <si>
     <t>Execute</t>
   </si>
@@ -827,7 +827,7 @@
     <t>Profile.docx</t>
   </si>
   <si>
-    <t>* ไฟล์ต้องเป็น .jpg, .jpeg, .png หรือ .gif เท่านั้น</t>
+    <t>ไฟล์ต้องเป็น .jpg, .jpeg, .png หรือ .gif เท่านั้น</t>
   </si>
   <si>
     <t>TC2:76</t>
@@ -857,7 +857,7 @@
     <t>Profile3.jpg</t>
   </si>
   <si>
-    <t>* ขนาดไฟล์ต้องไม่เกิน 5MB</t>
+    <t>ขนาดไฟล์ต้องไม่เกิน 5MB</t>
   </si>
   <si>
     <t>TC2:79</t>
@@ -866,7 +866,10 @@
     <t>MJU6504106454</t>
   </si>
   <si>
-    <t>* กรุณาเลือกไฟล์รูปภาพ</t>
+    <t>กรุณาเลือกไฟล์รูปภาพ</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -958,7 +961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -997,6 +1000,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -1325,20 +1346,20 @@
   <dimension ref="A1:N97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="18" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="18" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="19" width="8.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="20" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="18" width="10.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="18" width="19.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="18" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="18" width="9.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="18" width="48.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="18" width="41.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="24" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="25" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="24" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="25" width="8.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="26" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="24" width="10.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="24" width="19.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="24" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="24" width="9.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="24" width="48.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="24" width="41.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="24" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="24" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
@@ -2393,7 +2414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21.75">
       <c r="A25" s="4" t="s">
         <v>14</v>
       </c>
@@ -2437,7 +2458,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="21.75">
       <c r="A26" s="4" t="s">
         <v>14</v>
       </c>
@@ -2481,7 +2502,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="21.75">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2525,7 +2546,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="21.75">
       <c r="A28" s="4" t="s">
         <v>14</v>
       </c>
@@ -2569,7 +2590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="21.75">
       <c r="A29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2613,7 +2634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="21.75">
       <c r="A30" s="4" t="s">
         <v>14</v>
       </c>
@@ -2657,7 +2678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="21.75">
       <c r="A31" s="4" t="s">
         <v>14</v>
       </c>
@@ -2701,7 +2722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="21.75">
       <c r="A32" s="4" t="s">
         <v>14</v>
       </c>
@@ -2745,7 +2766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="21.75">
       <c r="A33" s="4" t="s">
         <v>14</v>
       </c>
@@ -2789,7 +2810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="21.75">
       <c r="A34" s="4" t="s">
         <v>14</v>
       </c>
@@ -4233,7 +4254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="21.75">
       <c r="A67" s="4" t="s">
         <v>14</v>
       </c>
@@ -4277,7 +4298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="21.75">
       <c r="A68" s="4" t="s">
         <v>14</v>
       </c>
@@ -4321,7 +4342,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="21.75">
       <c r="A69" s="4" t="s">
         <v>14</v>
       </c>
@@ -4365,7 +4386,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="21.75">
       <c r="A70" s="4" t="s">
         <v>14</v>
       </c>
@@ -4409,7 +4430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="21.75">
       <c r="A71" s="4" t="s">
         <v>14</v>
       </c>
@@ -4453,7 +4474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="21.75">
       <c r="A72" s="4" t="s">
         <v>14</v>
       </c>
@@ -4497,7 +4518,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="21.75">
       <c r="A73" s="4" t="s">
         <v>14</v>
       </c>
@@ -4541,7 +4562,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="21.75">
       <c r="A74" s="4" t="s">
         <v>14</v>
       </c>
@@ -4583,7 +4604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="21.75">
       <c r="A75" s="4" t="s">
         <v>14</v>
       </c>
@@ -4627,7 +4648,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="21.75">
       <c r="A76" s="4" t="s">
         <v>14</v>
       </c>
@@ -4671,7 +4692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="21.75">
       <c r="A77" s="4" t="s">
         <v>14</v>
       </c>
@@ -4803,7 +4824,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="21.75">
       <c r="A80" s="4" t="s">
         <v>14</v>
       </c>
@@ -4845,277 +4866,301 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
-      <c r="A81" s="14"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
-      <c r="M81" s="15"/>
-      <c r="N81" s="15"/>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="22.5">
+      <c r="A81" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="F81" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="G81" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J81" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="L81" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="M81" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="N81" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
-      <c r="A82" s="14"/>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="15"/>
-      <c r="K82" s="15"/>
-      <c r="L82" s="15"/>
-      <c r="M82" s="15"/>
-      <c r="N82" s="15"/>
+      <c r="A82" s="20"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="21"/>
+      <c r="K82" s="21"/>
+      <c r="L82" s="21"/>
+      <c r="M82" s="21"/>
+      <c r="N82" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
-      <c r="A83" s="14"/>
-      <c r="B83" s="15"/>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="15"/>
-      <c r="K83" s="15"/>
-      <c r="L83" s="15"/>
-      <c r="M83" s="15"/>
-      <c r="N83" s="15"/>
+      <c r="A83" s="20"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="21"/>
+      <c r="K83" s="21"/>
+      <c r="L83" s="21"/>
+      <c r="M83" s="21"/>
+      <c r="N83" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
-      <c r="A84" s="14"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="15"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="15"/>
-      <c r="K84" s="15"/>
-      <c r="L84" s="15"/>
-      <c r="M84" s="15"/>
-      <c r="N84" s="15"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="21"/>
+      <c r="K84" s="21"/>
+      <c r="L84" s="21"/>
+      <c r="M84" s="21"/>
+      <c r="N84" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
-      <c r="A85" s="14"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="16"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="15"/>
-      <c r="K85" s="15"/>
-      <c r="L85" s="15"/>
-      <c r="M85" s="15"/>
-      <c r="N85" s="15"/>
+      <c r="A85" s="20"/>
+      <c r="B85" s="21"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="21"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="21"/>
+      <c r="K85" s="21"/>
+      <c r="L85" s="21"/>
+      <c r="M85" s="21"/>
+      <c r="N85" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
-      <c r="A86" s="14"/>
-      <c r="B86" s="15"/>
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="16"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="15"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="15"/>
-      <c r="K86" s="15"/>
-      <c r="L86" s="15"/>
-      <c r="M86" s="15"/>
-      <c r="N86" s="15"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="21"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="21"/>
+      <c r="J86" s="21"/>
+      <c r="K86" s="21"/>
+      <c r="L86" s="21"/>
+      <c r="M86" s="21"/>
+      <c r="N86" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
-      <c r="A87" s="14"/>
-      <c r="B87" s="15"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="15"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
-      <c r="L87" s="15"/>
-      <c r="M87" s="15"/>
-      <c r="N87" s="15"/>
+      <c r="A87" s="20"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="21"/>
+      <c r="I87" s="21"/>
+      <c r="J87" s="21"/>
+      <c r="K87" s="21"/>
+      <c r="L87" s="21"/>
+      <c r="M87" s="21"/>
+      <c r="N87" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
-      <c r="A88" s="14"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="15"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="15"/>
-      <c r="K88" s="15"/>
-      <c r="L88" s="15"/>
-      <c r="M88" s="15"/>
-      <c r="N88" s="15"/>
+      <c r="A88" s="20"/>
+      <c r="B88" s="21"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="21"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="21"/>
+      <c r="H88" s="21"/>
+      <c r="I88" s="21"/>
+      <c r="J88" s="21"/>
+      <c r="K88" s="21"/>
+      <c r="L88" s="21"/>
+      <c r="M88" s="21"/>
+      <c r="N88" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
-      <c r="A89" s="14"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="15"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="15"/>
-      <c r="K89" s="15"/>
-      <c r="L89" s="15"/>
-      <c r="M89" s="15"/>
-      <c r="N89" s="15"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="21"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="21"/>
+      <c r="J89" s="21"/>
+      <c r="K89" s="21"/>
+      <c r="L89" s="21"/>
+      <c r="M89" s="21"/>
+      <c r="N89" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
-      <c r="A90" s="14"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="16"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="15"/>
-      <c r="K90" s="15"/>
-      <c r="L90" s="15"/>
-      <c r="M90" s="15"/>
-      <c r="N90" s="15"/>
+      <c r="A90" s="20"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="21"/>
+      <c r="H90" s="21"/>
+      <c r="I90" s="21"/>
+      <c r="J90" s="21"/>
+      <c r="K90" s="21"/>
+      <c r="L90" s="21"/>
+      <c r="M90" s="21"/>
+      <c r="N90" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
-      <c r="A91" s="14"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="15"/>
-      <c r="K91" s="15"/>
-      <c r="L91" s="15"/>
-      <c r="M91" s="15"/>
-      <c r="N91" s="15"/>
+      <c r="A91" s="20"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="21"/>
+      <c r="H91" s="21"/>
+      <c r="I91" s="21"/>
+      <c r="J91" s="21"/>
+      <c r="K91" s="21"/>
+      <c r="L91" s="21"/>
+      <c r="M91" s="21"/>
+      <c r="N91" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
-      <c r="A92" s="14"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="15"/>
-      <c r="M92" s="15"/>
-      <c r="N92" s="15"/>
+      <c r="A92" s="20"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="21"/>
+      <c r="H92" s="21"/>
+      <c r="I92" s="21"/>
+      <c r="J92" s="21"/>
+      <c r="K92" s="21"/>
+      <c r="L92" s="21"/>
+      <c r="M92" s="21"/>
+      <c r="N92" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
-      <c r="A93" s="14"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="16"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="15"/>
-      <c r="M93" s="15"/>
-      <c r="N93" s="15"/>
+      <c r="A93" s="20"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="21"/>
+      <c r="H93" s="21"/>
+      <c r="I93" s="21"/>
+      <c r="J93" s="21"/>
+      <c r="K93" s="21"/>
+      <c r="L93" s="21"/>
+      <c r="M93" s="21"/>
+      <c r="N93" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
-      <c r="A94" s="14"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="16"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="15"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="15"/>
-      <c r="K94" s="15"/>
-      <c r="L94" s="15"/>
-      <c r="M94" s="15"/>
-      <c r="N94" s="15"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="21"/>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="21"/>
+      <c r="I94" s="21"/>
+      <c r="J94" s="21"/>
+      <c r="K94" s="21"/>
+      <c r="L94" s="21"/>
+      <c r="M94" s="21"/>
+      <c r="N94" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
-      <c r="A95" s="14"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="15"/>
-      <c r="K95" s="15"/>
-      <c r="L95" s="15"/>
-      <c r="M95" s="15"/>
-      <c r="N95" s="15"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="21"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="21"/>
+      <c r="I95" s="21"/>
+      <c r="J95" s="21"/>
+      <c r="K95" s="21"/>
+      <c r="L95" s="21"/>
+      <c r="M95" s="21"/>
+      <c r="N95" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
-      <c r="A96" s="14"/>
-      <c r="B96" s="15"/>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="16"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="15"/>
-      <c r="K96" s="15"/>
-      <c r="L96" s="15"/>
-      <c r="M96" s="15"/>
-      <c r="N96" s="15"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="21"/>
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="21"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="21"/>
+      <c r="I96" s="21"/>
+      <c r="J96" s="21"/>
+      <c r="K96" s="21"/>
+      <c r="L96" s="21"/>
+      <c r="M96" s="21"/>
+      <c r="N96" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
-      <c r="A97" s="14"/>
-      <c r="B97" s="15"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
-      <c r="L97" s="15"/>
-      <c r="M97" s="15"/>
-      <c r="N97" s="15"/>
+      <c r="A97" s="20"/>
+      <c r="B97" s="21"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="21"/>
+      <c r="I97" s="21"/>
+      <c r="J97" s="21"/>
+      <c r="K97" s="21"/>
+      <c r="L97" s="21"/>
+      <c r="M97" s="21"/>
+      <c r="N97" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
